--- a/output/testing_result_databaru/ringkasan_testing.xlsx
+++ b/output/testing_result_databaru/ringkasan_testing.xlsx
@@ -478,28 +478,28 @@
         <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02009088734752451</v>
+        <v>0.01546856872771022</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4017336613086916</v>
+        <v>0.4158329258431651</v>
       </c>
       <c r="J2" t="n">
-        <v>1.020072156600759</v>
+        <v>1.090220706497434</v>
       </c>
     </row>
     <row r="3">
